--- a/xls/square_20_tri3_10.xlsx
+++ b/xls/square_20_tri3_10.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8">
+        <v>121</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8">
+        <v>441</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8">
+        <v>81</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8">
+        <v>384</v>
+      </c>
+      <c r="I8">
+        <v>21.785166597835197</v>
+      </c>
+      <c r="J8">
+        <v>11.203233270163278</v>
+      </c>
+      <c r="K8">
+        <v>8.35957900323949</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9">
+        <v>121</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9">
+        <v>441</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9">
+        <v>100</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9">
+        <v>486</v>
+      </c>
+      <c r="I9">
+        <v>4.672540928742657</v>
+      </c>
+      <c r="J9">
+        <v>1.3728507774274747</v>
+      </c>
+      <c r="K9">
+        <v>1.64572848128847</v>
+      </c>
+    </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
         <v>11</v>
